--- a/05_Figures/F06_prediction/proteins/T3/d_fcsa_II/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T3/d_fcsa_II/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -131,21 +131,21 @@
     <t xml:space="preserve">freq</t>
   </si>
   <si>
+    <t xml:space="preserve">PSMB5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPNT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP2K2</t>
+  </si>
+  <si>
     <t xml:space="preserve">MRPS18B</t>
   </si>
   <si>
-    <t xml:space="preserve">PSMB5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPNT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP2K2</t>
-  </si>
-  <si>
     <t xml:space="preserve">MYH3</t>
   </si>
   <si>
@@ -155,334 +155,340 @@
     <t xml:space="preserve">TGM2</t>
   </si>
   <si>
+    <t xml:space="preserve">DYNC1I2</t>
+  </si>
+  <si>
     <t xml:space="preserve">AK1</t>
   </si>
   <si>
-    <t xml:space="preserve">DYNC1I2</t>
+    <t xml:space="preserve">HK1</t>
   </si>
   <si>
     <t xml:space="preserve">SLC25A3</t>
   </si>
   <si>
+    <t xml:space="preserve">GLUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLVRA</t>
+  </si>
+  <si>
     <t xml:space="preserve">GPX1</t>
   </si>
   <si>
-    <t xml:space="preserve">HK1</t>
+    <t xml:space="preserve">PURA</t>
   </si>
   <si>
     <t xml:space="preserve">NAPRT</t>
   </si>
   <si>
-    <t xml:space="preserve">BLVRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLUL</t>
+    <t xml:space="preserve">PSME3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD23B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCDC43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCXR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHRS11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GORASP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HLA-DRA</t>
   </si>
   <si>
     <t xml:space="preserve">MGLL</t>
   </si>
   <si>
-    <t xml:space="preserve">HLA-DRA</t>
+    <t xml:space="preserve">ANXA3</t>
   </si>
   <si>
     <t xml:space="preserve">CD59</t>
   </si>
   <si>
-    <t xml:space="preserve">PURA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD23B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCDC43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCXR</t>
-  </si>
-  <si>
     <t xml:space="preserve">NARS1</t>
   </si>
   <si>
+    <t xml:space="preserve">RPA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL13A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TNPO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AQP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPZA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H1-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARVA</t>
+  </si>
+  <si>
     <t xml:space="preserve">PPM1A</t>
   </si>
   <si>
-    <t xml:space="preserve">RPL13A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TNPO3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AQP1</t>
+    <t xml:space="preserve">TKFC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USP15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCL2L13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BDH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPZB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERAP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MBNL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPLOC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELENBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMX4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBE2O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACAT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTN4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARF6</t>
   </si>
   <si>
     <t xml:space="preserve">ARHGAP19</t>
   </si>
   <si>
-    <t xml:space="preserve">CAPZA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPZB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSME3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TKFC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USP15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF5B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERAP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H1-5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MBNL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPLOC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELENBP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMX4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBE2O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BDH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDNF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHRS11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOOK3</t>
+    <t xml:space="preserve">ATP5MF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BDH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BROX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAB39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNG1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COQ10A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCAF8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDI2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIAPH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNC1H1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNC1LI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNLRB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECI2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESYT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNAI2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IARS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISCU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAMC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMS3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN2C1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTIF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NONO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUDT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OGDH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAFAH1B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDCD6IP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PKM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLIN3</t>
   </si>
   <si>
     <t xml:space="preserve">PMPCB</t>
   </si>
   <si>
+    <t xml:space="preserve">PPCS</t>
+  </si>
+  <si>
     <t xml:space="preserve">PPIF</t>
   </si>
   <si>
-    <t xml:space="preserve">PSMB2</t>
+    <t xml:space="preserve">PSMA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAB2B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBMX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL7A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCFD1</t>
   </si>
   <si>
     <t xml:space="preserve">SCRN3</t>
   </si>
   <si>
+    <t xml:space="preserve">SEC24C</t>
+  </si>
+  <si>
     <t xml:space="preserve">SFXN1</t>
   </si>
   <si>
+    <t xml:space="preserve">STK38L</t>
+  </si>
+  <si>
     <t xml:space="preserve">SYNE2</t>
   </si>
   <si>
-    <t xml:space="preserve">ACAT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARF6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5MF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCL2L13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BDH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLVRB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BROX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAB39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CACNG1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COQ10A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDI2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNC1H1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNC1LI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNLRB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPB41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESYT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FARSB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FTH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCLC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNAI2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISCU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAMC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIMS3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN2C1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTIF2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NONO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OGDH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAFAH1B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDCD6IP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIP4K2B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLIN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB2B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RBMX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL7A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCFD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC24C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STK38L</t>
+    <t xml:space="preserve">TACC2</t>
   </si>
   <si>
     <t xml:space="preserve">TBCA</t>
@@ -881,16 +887,16 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.03877107982311</v>
+        <v>-0.203107284728649</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0464285714285714</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -914,29 +920,21 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.03877107982311</v>
+        <v>-0.203107284728649</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0464285714285714</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.766169154228856</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.323383084577114</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.654191084029402</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.597664483211258</v>
-      </c>
+        <v>0.142857142857143</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -960,2206 +958,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-1.52725417340849</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-1.0668283277292</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.183622725077481</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-1.84577717767825</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.0277894780286587</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.46389175394465</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-1.3352541646874</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.685809510606759</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-1.00601589414212</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.64666297321168</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.138473749366717</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.382713090895237</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-1.34894597215976</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-1.10602800426055</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.268195212319933</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.782201200068707</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.221968800846005</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.14901814377684</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.101798379266975</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-0.72511035602906</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.6515768739649</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.372400233482492</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-0.541461404651978</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-2.18544156786859</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-0.802123863114788</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.00918361272461432</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.919922451753661</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-0.459141873466796</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-1.17749226144344</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.208809799871965</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-0.249888476483431</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-0.0648471108592399</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-0.835824661240768</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-1.10046523435648</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.189526628117057</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.198272098112106</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-0.333079835758568</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-0.869645484624054</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.42312202186401</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-1.09631662110074</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-1.06875685610384</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0.385751176917554</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-0.788387543470184</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0.303659600492629</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-1.10037640039496</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-0.600184624737748</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-2.10014388632835</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0.0434901619757697</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.740404394730933</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.979904922620651</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.673993762943113</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-0.111203436762893</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.443949332776903</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-0.912537547228473</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>0.383005474467802</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-1.16640563782463</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-1.41662261990215</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-1.29953520177753</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-1.12787559333898</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.139391585403539</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-0.684556077072651</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-0.949185593998844</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-0.281722408261362</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-0.769055709960386</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-0.206664712855798</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-0.715554265725147</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-0.538115133641226</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-1.82051869164089</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-0.26020286564346</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-0.585459075346455</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>0.335173580360217</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-0.558862194949543</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-1.10526489159074</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-0.330287177296421</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-0.57955675093162</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-0.489420055247802</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-1.4347911786595</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-1.04480447502099</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-0.408275484736254</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-0.68118213027145</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-0.640319560129793</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-2.72985407499531</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-1.2854748470926</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-0.743573597782467</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-0.429727668585632</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-0.504908596784277</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-0.894650452210612</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-0.731210006784457</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-0.666487795715465</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-0.41529764037685</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-1.10395536923302</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.0287229106717559</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-1.39616218370412</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-0.799687195805025</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-0.738147508350241</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-0.514994608254647</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-0.78037043182316</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-0.347154225298471</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-2.23924939170887</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-1.0656529722567</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-0.785925200759789</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-0.459626040680002</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.308159053819856</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-0.177717992730304</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-0.676798700310679</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-1.04668173934086</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-1.02295661585353</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.741528616280301</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-0.511802259465166</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-0.842105868940075</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-0.874941553542735</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-1.79340067987733</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-0.70195041540801</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-1.1377365599998</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-0.767698358743348</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-3.43449964431372</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-1.09942114303851</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-1.48216333141474</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-1.05508489244541</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-0.606894429508475</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-0.200735650563309</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-0.334440483389922</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-0.295470139315691</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>0.0365337600998195</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-0.687450986170445</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-0.929152223872497</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.38682641334154</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-0.790362472655667</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-0.786024368863316</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>0.371505387091016</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-1.1544906205125</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.752615829526879</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-1.28021401604466</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-0.688929031459384</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-0.565964821000017</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-0.678064591136782</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>0.11863097545263</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-1.05461780661769</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-0.189070569251393</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>0.0173408343510717</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-0.394642497246639</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-0.19581258939053</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-0.00369508500839433</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.375952669439104</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-0.852734205210058</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.967545054872661</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>0.0574772066822343</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-0.94904795840327</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-1.23235274157756</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.257865441239504</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-2.36043348989815</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-0.0777277739255906</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-0.224837856551827</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-0.26771910301915</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-0.347624049414511</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-0.30719116111095</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-0.654669042119323</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-0.982531103564916</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-0.591183462852554</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-0.81712656696636</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-1.37255832821467</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.881761333492161</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.438149848093412</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-0.626569353574152</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.422636625041888</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-1.23432205062043</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.629666925502568</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-0.409136823677732</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-1.15790516993186</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-0.752031148181019</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-0.43592624895339</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-0.154723785809564</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-1.77037439302296</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>0.123627509713204</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-0.0752591551741413</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.475803019705605</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-0.683061343357334</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-0.586846979374288</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>0.0858009994398088</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>0.261813458523003</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>0.0509470220631545</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>0.401834536488011</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-0.961436881899998</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>0.120363608669201</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-0.351216207115748</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>0.277588644365684</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-0.294805972902403</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>-0.424655215925783</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-0.4691513072172</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>-0.855961011904225</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-1.33973013194881</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-1.15019680999976</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-0.983435512977102</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-0.602707971046558</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-0.0851643586737498</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-0.723676792853949</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>0.119102877009888</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-1.50354464150865</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-0.155431220466318</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-0.384915408342173</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3202,7 +1000,7 @@
         <v>517.34</v>
       </c>
       <c r="E2" t="n">
-        <v>718.645687419435</v>
+        <v>681.79219103504</v>
       </c>
     </row>
     <row r="3">
@@ -3219,7 +1017,7 @@
         <v>1517.85</v>
       </c>
       <c r="E3" t="n">
-        <v>-346.751316703854</v>
+        <v>-222.584980499825</v>
       </c>
     </row>
     <row r="4">
@@ -3236,7 +1034,7 @@
         <v>2790.83</v>
       </c>
       <c r="E4" t="n">
-        <v>207.693922656992</v>
+        <v>217.199588926028</v>
       </c>
     </row>
     <row r="5">
@@ -3253,7 +1051,7 @@
         <v>739.459999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-1408.53515004054</v>
+        <v>-1393.39895434189</v>
       </c>
     </row>
     <row r="6">
@@ -3270,7 +1068,7 @@
         <v>1179</v>
       </c>
       <c r="E6" t="n">
-        <v>-3605.66441883795</v>
+        <v>-522.629975779291</v>
       </c>
     </row>
     <row r="7">
@@ -3287,7 +1085,7 @@
         <v>682.55</v>
       </c>
       <c r="E7" t="n">
-        <v>1422.49391628794</v>
+        <v>1387.02617877943</v>
       </c>
     </row>
     <row r="8">
@@ -3304,7 +1102,7 @@
         <v>35.9499999999998</v>
       </c>
       <c r="E8" t="n">
-        <v>-962.041371010895</v>
+        <v>-1036.12664407607</v>
       </c>
     </row>
     <row r="9">
@@ -3321,7 +1119,7 @@
         <v>-171.76</v>
       </c>
       <c r="E9" t="n">
-        <v>472.019600422554</v>
+        <v>479.532171167788</v>
       </c>
     </row>
     <row r="10">
@@ -3338,7 +1136,7 @@
         <v>854.04</v>
       </c>
       <c r="E10" t="n">
-        <v>649.197233824696</v>
+        <v>944.451493099457</v>
       </c>
     </row>
     <row r="11">
@@ -3355,7 +1153,7 @@
         <v>-1503.6</v>
       </c>
       <c r="E11" t="n">
-        <v>121.42899020853</v>
+        <v>98.9806808021017</v>
       </c>
     </row>
     <row r="12">
@@ -3372,7 +1170,7 @@
         <v>-88.7199999999993</v>
       </c>
       <c r="E12" t="n">
-        <v>-489.596514337728</v>
+        <v>-454.298608087934</v>
       </c>
     </row>
     <row r="13">
@@ -3389,7 +1187,7 @@
         <v>-2305.05</v>
       </c>
       <c r="E13" t="n">
-        <v>189.545357625886</v>
+        <v>156.719464364616</v>
       </c>
     </row>
     <row r="14">
@@ -3406,7 +1204,7 @@
         <v>-1179.58</v>
       </c>
       <c r="E14" t="n">
-        <v>-1034.29535558797</v>
+        <v>-1052.47024616016</v>
       </c>
     </row>
     <row r="15">
@@ -3423,7 +1221,7 @@
         <v>-1491.94</v>
       </c>
       <c r="E15" t="n">
-        <v>-190.360277753887</v>
+        <v>-218.339205747444</v>
       </c>
     </row>
     <row r="16">
@@ -3440,7 +1238,7 @@
         <v>-1081</v>
       </c>
       <c r="E16" t="n">
-        <v>-2602.846242657</v>
+        <v>-2316.75622765485</v>
       </c>
     </row>
   </sheetData>
@@ -3482,10 +1280,10 @@
         <v>38</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>0.933333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3499,10 +1297,10 @@
         <v>39</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>0.933333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3533,10 +1331,10 @@
         <v>41</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -3550,10 +1348,10 @@
         <v>42</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -3567,10 +1365,10 @@
         <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -3584,10 +1382,10 @@
         <v>44</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -3601,10 +1399,10 @@
         <v>45</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0.866666666666667</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10">
@@ -3618,10 +1416,10 @@
         <v>46</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -3635,10 +1433,10 @@
         <v>47</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="12">
@@ -3652,10 +1450,10 @@
         <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -3669,10 +1467,10 @@
         <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0.733333333333333</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -3686,10 +1484,10 @@
         <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>0.733333333333333</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15">
@@ -3703,10 +1501,10 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>0.733333333333333</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="16">
@@ -3720,10 +1518,10 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>0.666666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="17">
@@ -3737,10 +1535,10 @@
         <v>53</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>0.666666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="18">
@@ -3754,10 +1552,10 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>0.666666666666667</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="19">
@@ -3771,10 +1569,10 @@
         <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>0.533333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="20">
@@ -3788,10 +1586,10 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>0.466666666666667</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="21">
@@ -3805,10 +1603,10 @@
         <v>57</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>0.466666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="22">
@@ -3822,10 +1620,10 @@
         <v>58</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>0.466666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="23">
@@ -3839,10 +1637,10 @@
         <v>59</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="24">
@@ -3907,10 +1705,10 @@
         <v>63</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>0.333333333333333</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="28">
@@ -3924,10 +1722,10 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>0.333333333333333</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="29">
@@ -3941,10 +1739,10 @@
         <v>65</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>0.333333333333333</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="30">
@@ -4009,10 +1807,10 @@
         <v>69</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>0.266666666666667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="34">
@@ -4026,10 +1824,10 @@
         <v>70</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>0.266666666666667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="35">
@@ -4043,10 +1841,10 @@
         <v>71</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>0.266666666666667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="36">
@@ -4060,10 +1858,10 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>0.266666666666667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="37">
@@ -4077,10 +1875,10 @@
         <v>73</v>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>0.266666666666667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="38">
@@ -4094,10 +1892,10 @@
         <v>74</v>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>0.266666666666667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="39">
@@ -4145,10 +1943,10 @@
         <v>77</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="42">
@@ -4162,10 +1960,10 @@
         <v>78</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="43">
@@ -4179,10 +1977,10 @@
         <v>79</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="44">
@@ -4196,10 +1994,10 @@
         <v>80</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="45">
@@ -4213,10 +2011,10 @@
         <v>81</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="46">
@@ -4230,10 +2028,10 @@
         <v>82</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="47">
@@ -4247,10 +2045,10 @@
         <v>83</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="48">
@@ -4264,10 +2062,10 @@
         <v>84</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="49">
@@ -4383,10 +2181,10 @@
         <v>91</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="56">
@@ -4400,10 +2198,10 @@
         <v>92</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="57">
@@ -4417,10 +2215,10 @@
         <v>93</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="58">
@@ -4434,10 +2232,10 @@
         <v>94</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="59">
@@ -4451,10 +2249,10 @@
         <v>95</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="60">
@@ -4468,10 +2266,10 @@
         <v>96</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="61">
@@ -5542,6 +3340,40 @@
         <v>1</v>
       </c>
       <c r="E123" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="s">
+        <v>160</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="s">
+        <v>161</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="n">
         <v>0.0666666666666667</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/T3/d_fcsa_II/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T3/d_fcsa_II/spls/c_data/results.xlsx
@@ -923,7 +923,7 @@
         <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.203107284728649</v>
@@ -931,10 +931,18 @@
       <c r="I3" t="n">
         <v>0.142857142857143</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.233830845771144</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.248756218905473</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.668356628576269</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.610131541313643</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -958,6 +966,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.51037586561986</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.0473063872045</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.0263098285736429</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.68192530909932</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0388950983214975</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.568903103091166</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.14497407974424</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.463041640017704</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.22793466385958</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.42839286377667</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0560281654642293</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.304292298955404</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.28748576932077</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.96665081960316</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.174595486304876</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.821653274035318</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.19334526439872</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.137703991209335</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.314936530200665</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.967566302869285</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.878556675247685</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-1.55166463480107</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.647654651528341</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-2.09594851216364</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.756664632737506</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.0125356794594425</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.934576999905625</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.542319143589418</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-1.7229430920158</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.15027910890924</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.239322275213418</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.0637540244732286</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-1.01360228409949</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.906146723027494</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.194619188948166</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.160372671763251</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.32022001556682</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.693761077564838</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.531626717202868</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-1.07102589856325</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-1.33767620483224</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.383027879598558</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.564364921932999</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.262010493472517</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.918944830092795</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.623011755959718</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-2.14889600456276</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.0450511709859768</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.370797654008264</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-1.08164907269649</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.663116911707946</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.0577766540543005</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.462971205898</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.814603066480802</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.385885303444398</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-1.19590767557792</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-1.54028863575202</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.997916914034651</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.748908271451433</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.163182355288301</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.806319904253732</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.893176422628249</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.68630753734244</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.774335527919324</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.305419224482029</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.531438896362303</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.89605901632629</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-1.81558358905759</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.229353611413542</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.488826239187317</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.290473326885711</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.52063605912895</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-1.38515547927412</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.16867780010559</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-0.254272066980754</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-0.230448947556487</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-1.40532768902306</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-1.20516807793251</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.548161390107311</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-1.49776867588804</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.558865668371185</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-2.65495850559288</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-1.14495762625401</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.707390684171984</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.379037249796503</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.532253798624799</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-0.685342832813303</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.518642010864216</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.620558083982427</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-0.432793701476515</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-1.14770517841619</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.0640382380568079</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-1.5362637375166</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-0.540570166039977</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-0.799967719281024</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-0.627461163864027</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.768956210600824</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.457821277394476</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-2.58949714292019</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-1.20628961154816</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-0.710016126643192</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.225920811517101</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.423644932080456</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-0.109184560951237</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.603090166232502</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-0.936407353981577</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-1.28399493307904</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.645053974089428</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.493587811860963</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-0.691761454939092</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-1.05246536756665</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.853022428009848</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.600131741736553</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-1.37563322681421</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.758812707566252</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-3.6956972258712</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.79282584559826</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-1.46137705035173</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-1.25927251484557</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.584292995676914</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.201789984365528</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-0.1759959458205</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.30969463373471</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.0368929162881653</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.746992905577228</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-1.19150019301688</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.469424945767608</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.957241043082778</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.81112362619835</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.377107657816728</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-1.03596441935791</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.605205161939871</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-1.16687440761544</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-1.40417476897699</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.456361099973701</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.728520429914839</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.184848982573814</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-1.19335859249316</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-0.114289478102683</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.00378617358064559</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.448153241914488</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.226719488274394</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0.0360224153989693</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.241149120989584</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-0.794133105449483</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.961662080370111</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0.0378002604160189</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-1.00165884805216</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-1.22509619000926</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.281665115009796</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-1.71718212182905</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.0469284111812189</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.0705239645603029</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.838081655319797</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-0.702213653403607</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.200521595474972</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-1.03381389770049</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-0.873914141686237</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.568587793602748</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-0.540798423310003</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-1.30746766557753</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.505500458528301</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.489788124069643</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.568754408215338</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.451504816469241</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-1.19889609296152</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.642403306929968</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.371119134465134</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-1.29430215657716</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.803901196522608</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-0.429769446676827</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-0.0277958537791132</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-1.70499981975515</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0.138735228922997</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0.2583350588957</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.644687276620409</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-1.06378230647212</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-0.673303326274606</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.0125855987367179</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.167581823727378</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0.0555675016572847</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0.404387253460581</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-0.865184229555157</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-0.136109200054246</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-0.41576297055914</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0.298414719577208</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.410922435453362</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-0.661850414252107</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-0.479211337943098</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-0.934351013328146</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-1.43638111188794</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.771498579771696</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-1.0528521445134</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.767233853233196</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-0.489064509136012</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-0.96857799784156</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.171992770384262</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-1.70165799654567</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.196232519476859</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.356467369988041</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
